--- a/src/final_selected_features_report_0323.xlsx
+++ b/src/final_selected_features_report_0323.xlsx
@@ -7284,7 +7284,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>00_[-inf, 0.236)</t>
+          <t>00_[-inf, 0.2364)</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>01_[0.236, 1.1)</t>
+          <t>01_[0.2364, 1.1034)</t>
         </is>
       </c>
       <c r="G21" s="4" t="n">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>02_[1.1, 1.72)</t>
+          <t>02_[1.1034, 1.7159)</t>
         </is>
       </c>
       <c r="G22" s="4" t="n">
@@ -7469,7 +7469,7 @@
         <v>0.01081081081080107</v>
       </c>
       <c r="P22" s="33" t="n">
-        <v>-1.030196951017641e-12</v>
+        <v>-1.030196950910897e-12</v>
       </c>
       <c r="Q22" s="33" t="n">
         <v>33.67416165723135</v>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>03_[1.72, 2.35)</t>
+          <t>03_[1.7159, 2.3529)</t>
         </is>
       </c>
       <c r="G23" s="4" t="n">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>04_[2.35, 2.86)</t>
+          <t>04_[2.3529, 2.8603)</t>
         </is>
       </c>
       <c r="G24" s="4" t="n">
@@ -7623,7 +7623,7 @@
         <v>0.02340550029255506</v>
       </c>
       <c r="P24" s="33" t="n">
-        <v>-1.047252332270467e-12</v>
+        <v>-1.047252332143111e-12</v>
       </c>
       <c r="Q24" s="33" t="n">
         <v>44.70989211417821</v>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>05_[2.86, 3.75)</t>
+          <t>05_[2.8603, 3.7545)</t>
         </is>
       </c>
       <c r="G25" s="4" t="n">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>06_[3.75, 4.53)</t>
+          <t>06_[3.7545, 4.5272)</t>
         </is>
       </c>
       <c r="G26" s="4" t="n">
@@ -7777,7 +7777,7 @@
         <v>0.04775993237529681</v>
       </c>
       <c r="P26" s="33" t="n">
-        <v>-1.039942908969422e-12</v>
+        <v>-1.039942908851512e-12</v>
       </c>
       <c r="Q26" s="33" t="n">
         <v>46.04413010302695</v>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>07_[4.53, 5.58)</t>
+          <t>07_[4.5272, 5.5781)</t>
         </is>
       </c>
       <c r="G27" s="4" t="n">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>08_[5.58, inf)</t>
+          <t>08_[5.5781, inf)</t>
         </is>
       </c>
       <c r="G28" s="4" t="n">
@@ -7931,7 +7931,7 @@
         <v>0.1058069112931579</v>
       </c>
       <c r="P28" s="33" t="n">
-        <v>-1.070154840836719e-12</v>
+        <v>-1.070154840680869e-12</v>
       </c>
       <c r="Q28" s="33" t="n">
         <v>2.636977414205433e-07</v>
@@ -8085,7 +8085,7 @@
         <v>0.1023142509134889</v>
       </c>
       <c r="P30" s="33" t="n">
-        <v>-5.241621451444639e-12</v>
+        <v>-5.241621450936779e-12</v>
       </c>
       <c r="Q30" s="33" t="n">
         <v>50.61421794162599</v>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>00_[-inf, 0.236)</t>
+          <t>00_[-inf, 0.2364)</t>
         </is>
       </c>
       <c r="G31" s="4" t="n">
@@ -8162,7 +8162,7 @@
         <v>0.004237288135584243</v>
       </c>
       <c r="P31" s="33" t="n">
-        <v>6.724703723634658e-07</v>
+        <v>6.724703723635588e-07</v>
       </c>
       <c r="Q31" s="33" t="n">
         <v>14.52484178611526</v>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>01_[0.236, 1.1)</t>
+          <t>01_[0.2364, 1.1034)</t>
         </is>
       </c>
       <c r="G32" s="4" t="n">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>02_[1.1, 1.72)</t>
+          <t>02_[1.1034, 1.7159)</t>
         </is>
       </c>
       <c r="G33" s="4" t="n">
@@ -8316,7 +8316,7 @@
         <v>0.01367521367520199</v>
       </c>
       <c r="P33" s="33" t="n">
-        <v>0.001324593892251495</v>
+        <v>0.001324593892251493</v>
       </c>
       <c r="Q33" s="33" t="n">
         <v>31.91671620492527</v>
@@ -8362,7 +8362,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>03_[1.72, 2.35)</t>
+          <t>03_[1.7159, 2.3529)</t>
         </is>
       </c>
       <c r="G34" s="4" t="n">
@@ -8393,7 +8393,7 @@
         <v>0.01605351170567488</v>
       </c>
       <c r="P34" s="33" t="n">
-        <v>0.0008653665778200217</v>
+        <v>0.0008653665778200239</v>
       </c>
       <c r="Q34" s="33" t="n">
         <v>39.46627741489399</v>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>04_[2.35, 2.86)</t>
+          <t>04_[2.3529, 2.8603)</t>
         </is>
       </c>
       <c r="G35" s="4" t="n">
@@ -8470,7 +8470,7 @@
         <v>0.01923076923075836</v>
       </c>
       <c r="P35" s="33" t="n">
-        <v>0.0004158988771816172</v>
+        <v>0.000415898877181615</v>
       </c>
       <c r="Q35" s="33" t="n">
         <v>44.59372051995175</v>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>05_[2.86, 3.75)</t>
+          <t>05_[2.8603, 3.7545)</t>
         </is>
       </c>
       <c r="G36" s="4" t="n">
@@ -8547,7 +8547,7 @@
         <v>0.0336250575771379</v>
       </c>
       <c r="P36" s="33" t="n">
-        <v>2.469614786518073e-05</v>
+        <v>2.469614786517995e-05</v>
       </c>
       <c r="Q36" s="33" t="n">
         <v>43.19036053827999</v>
@@ -8593,7 +8593,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>06_[3.75, 4.53)</t>
+          <t>06_[3.7545, 4.5272)</t>
         </is>
       </c>
       <c r="G37" s="4" t="n">
@@ -8624,7 +8624,7 @@
         <v>0.04197530864195804</v>
       </c>
       <c r="P37" s="33" t="n">
-        <v>0.0001764937049853171</v>
+        <v>0.0001764937049853186</v>
       </c>
       <c r="Q37" s="33" t="n">
         <v>40.30103856700824</v>
@@ -8670,7 +8670,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>07_[4.53, 5.58)</t>
+          <t>07_[4.5272, 5.5781)</t>
         </is>
       </c>
       <c r="G38" s="4" t="n">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>08_[5.58, inf)</t>
+          <t>08_[5.5781, inf)</t>
         </is>
       </c>
       <c r="G39" s="4" t="n">
@@ -8778,7 +8778,7 @@
         <v>0.08686514886161581</v>
       </c>
       <c r="P39" s="33" t="n">
-        <v>0.0005394325788980389</v>
+        <v>0.0005394325788980417</v>
       </c>
       <c r="Q39" s="33" t="n">
         <v>3.054963171322811e-07</v>
@@ -8932,7 +8932,7 @@
         <v>0.08736717827624339</v>
       </c>
       <c r="P41" s="33" t="n">
-        <v>0.003459721863298501</v>
+        <v>0.003459721863298503</v>
       </c>
       <c r="Q41" s="33" t="n">
         <v>44.59372051995175</v>
@@ -8978,7 +8978,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>00_[-inf, 0.236)</t>
+          <t>00_[-inf, 0.2364)</t>
         </is>
       </c>
       <c r="G42" s="4" t="n">
@@ -9009,7 +9009,7 @@
         <v>0.005836575875475026</v>
       </c>
       <c r="P42" s="33" t="n">
-        <v>0.001736087251765199</v>
+        <v>0.001736087251765193</v>
       </c>
       <c r="Q42" s="33" t="n">
         <v>16.12715889808134</v>
@@ -9055,7 +9055,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>01_[0.236, 1.1)</t>
+          <t>01_[0.2364, 1.1034)</t>
         </is>
       </c>
       <c r="G43" s="4" t="n">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>02_[1.1, 1.72)</t>
+          <t>02_[1.1034, 1.7159)</t>
         </is>
       </c>
       <c r="G44" s="4" t="n">
@@ -9163,7 +9163,7 @@
         <v>0.01429772918417637</v>
       </c>
       <c r="P44" s="33" t="n">
-        <v>0.001128377915005526</v>
+        <v>0.001128377915005525</v>
       </c>
       <c r="Q44" s="33" t="n">
         <v>33.91251998147218</v>
@@ -9209,7 +9209,7 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>03_[1.72, 2.35)</t>
+          <t>03_[1.7159, 2.3529)</t>
         </is>
       </c>
       <c r="G45" s="4" t="n">
@@ -9240,7 +9240,7 @@
         <v>0.02292650033713896</v>
       </c>
       <c r="P45" s="33" t="n">
-        <v>0.003257163253097072</v>
+        <v>0.003257163253097077</v>
       </c>
       <c r="Q45" s="33" t="n">
         <v>37.98175887919754</v>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>04_[2.35, 2.86)</t>
+          <t>04_[2.3529, 2.8603)</t>
         </is>
       </c>
       <c r="G46" s="4" t="n">
@@ -9317,7 +9317,7 @@
         <v>0.02731929425154962</v>
       </c>
       <c r="P46" s="33" t="n">
-        <v>0.0007123663543206875</v>
+        <v>0.0007123663543206845</v>
       </c>
       <c r="Q46" s="33" t="n">
         <v>42.39599625914426</v>
@@ -9363,7 +9363,7 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>05_[2.86, 3.75)</t>
+          <t>05_[2.8603, 3.7545)</t>
         </is>
       </c>
       <c r="G47" s="4" t="n">
@@ -9394,7 +9394,7 @@
         <v>0.03734827264237285</v>
       </c>
       <c r="P47" s="33" t="n">
-        <v>3.459965780581079e-05</v>
+        <v>3.459965780581173e-05</v>
       </c>
       <c r="Q47" s="33" t="n">
         <v>44.44014271251836</v>
@@ -9440,7 +9440,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>06_[3.75, 4.53)</t>
+          <t>06_[3.7545, 4.5272)</t>
         </is>
       </c>
       <c r="G48" s="4" t="n">
@@ -9471,7 +9471,7 @@
         <v>0.0470637234485435</v>
       </c>
       <c r="P48" s="33" t="n">
-        <v>6.830132726200289e-05</v>
+        <v>6.830132726200356e-05</v>
       </c>
       <c r="Q48" s="33" t="n">
         <v>38.03506957265319</v>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>07_[4.53, 5.58)</t>
+          <t>07_[4.5272, 5.5781)</t>
         </is>
       </c>
       <c r="G49" s="4" t="n">
@@ -9594,7 +9594,7 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>08_[5.58, inf)</t>
+          <t>08_[5.5781, inf)</t>
         </is>
       </c>
       <c r="G50" s="4" t="n">
@@ -9625,7 +9625,7 @@
         <v>0.09472934472931099</v>
       </c>
       <c r="P50" s="33" t="n">
-        <v>0.0004696197169115931</v>
+        <v>0.0004696197169115956</v>
       </c>
       <c r="Q50" s="33" t="n">
         <v>2.706069257563115e-07</v>
@@ -9825,7 +9825,7 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>00_[-inf, 0.236)</t>
+          <t>00_[-inf, 0.2364)</t>
         </is>
       </c>
       <c r="G53" s="4" t="n">
@@ -9902,7 +9902,7 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>01_[0.236, 1.1)</t>
+          <t>01_[0.2364, 1.1034)</t>
         </is>
       </c>
       <c r="G54" s="4" t="n">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>02_[1.1, 1.72)</t>
+          <t>02_[1.1034, 1.7159)</t>
         </is>
       </c>
       <c r="G55" s="4" t="n">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>03_[1.72, 2.35)</t>
+          <t>03_[1.7159, 2.3529)</t>
         </is>
       </c>
       <c r="G56" s="4" t="n">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>04_[2.35, 2.86)</t>
+          <t>04_[2.3529, 2.8603)</t>
         </is>
       </c>
       <c r="G57" s="4" t="n">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>05_[2.86, 3.75)</t>
+          <t>05_[2.8603, 3.7545)</t>
         </is>
       </c>
       <c r="G58" s="4" t="n">
@@ -10287,7 +10287,7 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>06_[3.75, 4.53)</t>
+          <t>06_[3.7545, 4.5272)</t>
         </is>
       </c>
       <c r="G59" s="4" t="n">
@@ -10364,7 +10364,7 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>07_[4.53, 5.58)</t>
+          <t>07_[4.5272, 5.5781)</t>
         </is>
       </c>
       <c r="G60" s="4" t="n">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>08_[5.58, inf)</t>
+          <t>08_[5.5781, inf)</t>
         </is>
       </c>
       <c r="G61" s="4" t="n">
@@ -10672,7 +10672,7 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>00_[-inf, -0.617)</t>
+          <t>00_[-inf, -0.6172)</t>
         </is>
       </c>
       <c r="G64" s="4" t="n">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>01_[-0.617, 1.27)</t>
+          <t>01_[-0.6172, 1.2717)</t>
         </is>
       </c>
       <c r="G65" s="4" t="n">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>02_[1.27, 1.84)</t>
+          <t>02_[1.2717, 1.841)</t>
         </is>
       </c>
       <c r="G66" s="4" t="n">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>03_[1.84, 2.41)</t>
+          <t>03_[1.841, 2.4138)</t>
         </is>
       </c>
       <c r="G67" s="4" t="n">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>04_[2.41, 2.83)</t>
+          <t>04_[2.4138, 2.8293)</t>
         </is>
       </c>
       <c r="G68" s="4" t="n">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>05_[2.83, 3.52)</t>
+          <t>05_[2.8293, 3.5163)</t>
         </is>
       </c>
       <c r="G69" s="4" t="n">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>06_[3.52, 4.02)</t>
+          <t>06_[3.5163, 4.0212)</t>
         </is>
       </c>
       <c r="G70" s="4" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>07_[4.02, 4.69)</t>
+          <t>07_[4.0212, 4.6948)</t>
         </is>
       </c>
       <c r="G71" s="4" t="n">
@@ -11288,7 +11288,7 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>08_[4.69, 5.86)</t>
+          <t>08_[4.6948, 5.8594)</t>
         </is>
       </c>
       <c r="G72" s="4" t="n">
@@ -11365,7 +11365,7 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>09_[5.86, inf)</t>
+          <t>09_[5.8594, inf)</t>
         </is>
       </c>
       <c r="G73" s="4" t="n">
@@ -11519,7 +11519,7 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>00_[-inf, -0.617)</t>
+          <t>00_[-inf, -0.6172)</t>
         </is>
       </c>
       <c r="G75" s="4" t="n">
@@ -11596,7 +11596,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>01_[-0.617, 1.27)</t>
+          <t>01_[-0.6172, 1.2717)</t>
         </is>
       </c>
       <c r="G76" s="4" t="n">
@@ -11673,7 +11673,7 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>02_[1.27, 1.84)</t>
+          <t>02_[1.2717, 1.841)</t>
         </is>
       </c>
       <c r="G77" s="4" t="n">
@@ -11750,7 +11750,7 @@
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>03_[1.84, 2.41)</t>
+          <t>03_[1.841, 2.4138)</t>
         </is>
       </c>
       <c r="G78" s="4" t="n">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>04_[2.41, 2.83)</t>
+          <t>04_[2.4138, 2.8293)</t>
         </is>
       </c>
       <c r="G79" s="4" t="n">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>05_[2.83, 3.52)</t>
+          <t>05_[2.8293, 3.5163)</t>
         </is>
       </c>
       <c r="G80" s="4" t="n">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>06_[3.52, 4.02)</t>
+          <t>06_[3.5163, 4.0212)</t>
         </is>
       </c>
       <c r="G81" s="4" t="n">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>07_[4.02, 4.69)</t>
+          <t>07_[4.0212, 4.6948)</t>
         </is>
       </c>
       <c r="G82" s="4" t="n">
@@ -12135,7 +12135,7 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>08_[4.69, 5.86)</t>
+          <t>08_[4.6948, 5.8594)</t>
         </is>
       </c>
       <c r="G83" s="4" t="n">
@@ -12212,7 +12212,7 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>09_[5.86, inf)</t>
+          <t>09_[5.8594, inf)</t>
         </is>
       </c>
       <c r="G84" s="4" t="n">
@@ -12366,7 +12366,7 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>00_[-inf, -0.617)</t>
+          <t>00_[-inf, -0.6172)</t>
         </is>
       </c>
       <c r="G86" s="4" t="n">
@@ -12443,7 +12443,7 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>01_[-0.617, 1.27)</t>
+          <t>01_[-0.6172, 1.2717)</t>
         </is>
       </c>
       <c r="G87" s="4" t="n">
@@ -12520,7 +12520,7 @@
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>02_[1.27, 1.84)</t>
+          <t>02_[1.2717, 1.841)</t>
         </is>
       </c>
       <c r="G88" s="4" t="n">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>03_[1.84, 2.41)</t>
+          <t>03_[1.841, 2.4138)</t>
         </is>
       </c>
       <c r="G89" s="4" t="n">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>04_[2.41, 2.83)</t>
+          <t>04_[2.4138, 2.8293)</t>
         </is>
       </c>
       <c r="G90" s="4" t="n">
@@ -12751,7 +12751,7 @@
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>05_[2.83, 3.52)</t>
+          <t>05_[2.8293, 3.5163)</t>
         </is>
       </c>
       <c r="G91" s="4" t="n">
@@ -12828,7 +12828,7 @@
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>06_[3.52, 4.02)</t>
+          <t>06_[3.5163, 4.0212)</t>
         </is>
       </c>
       <c r="G92" s="4" t="n">
@@ -12905,7 +12905,7 @@
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>07_[4.02, 4.69)</t>
+          <t>07_[4.0212, 4.6948)</t>
         </is>
       </c>
       <c r="G93" s="4" t="n">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>08_[4.69, 5.86)</t>
+          <t>08_[4.6948, 5.8594)</t>
         </is>
       </c>
       <c r="G94" s="4" t="n">
@@ -13059,7 +13059,7 @@
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>09_[5.86, inf)</t>
+          <t>09_[5.8594, inf)</t>
         </is>
       </c>
       <c r="G95" s="4" t="n">
@@ -13213,7 +13213,7 @@
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>00_[-inf, -0.617)</t>
+          <t>00_[-inf, -0.6172)</t>
         </is>
       </c>
       <c r="G97" s="4" t="n">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>01_[-0.617, 1.27)</t>
+          <t>01_[-0.6172, 1.2717)</t>
         </is>
       </c>
       <c r="G98" s="4" t="n">
@@ -13367,7 +13367,7 @@
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>02_[1.27, 1.84)</t>
+          <t>02_[1.2717, 1.841)</t>
         </is>
       </c>
       <c r="G99" s="4" t="n">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>03_[1.84, 2.41)</t>
+          <t>03_[1.841, 2.4138)</t>
         </is>
       </c>
       <c r="G100" s="4" t="n">
@@ -13521,7 +13521,7 @@
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>04_[2.41, 2.83)</t>
+          <t>04_[2.4138, 2.8293)</t>
         </is>
       </c>
       <c r="G101" s="4" t="n">
@@ -13598,7 +13598,7 @@
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>05_[2.83, 3.52)</t>
+          <t>05_[2.8293, 3.5163)</t>
         </is>
       </c>
       <c r="G102" s="4" t="n">
@@ -13675,7 +13675,7 @@
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>06_[3.52, 4.02)</t>
+          <t>06_[3.5163, 4.0212)</t>
         </is>
       </c>
       <c r="G103" s="4" t="n">
@@ -13752,7 +13752,7 @@
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>07_[4.02, 4.69)</t>
+          <t>07_[4.0212, 4.6948)</t>
         </is>
       </c>
       <c r="G104" s="4" t="n">
@@ -13829,7 +13829,7 @@
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>08_[4.69, 5.86)</t>
+          <t>08_[4.6948, 5.8594)</t>
         </is>
       </c>
       <c r="G105" s="4" t="n">
@@ -13906,7 +13906,7 @@
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>09_[5.86, inf)</t>
+          <t>09_[5.8594, inf)</t>
         </is>
       </c>
       <c r="G106" s="4" t="n">
@@ -14060,7 +14060,7 @@
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>00_[-inf, -1.23)</t>
+          <t>00_[-inf, -1.2323)</t>
         </is>
       </c>
       <c r="G108" s="4" t="n">
@@ -14137,7 +14137,7 @@
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>01_[-1.23, -0.766)</t>
+          <t>01_[-1.2323, -0.7665)</t>
         </is>
       </c>
       <c r="G109" s="4" t="n">
@@ -14214,7 +14214,7 @@
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>02_[-0.766, 1.41)</t>
+          <t>02_[-0.7665, 1.4143)</t>
         </is>
       </c>
       <c r="G110" s="4" t="n">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>03_[1.41, inf)</t>
+          <t>03_[1.4143, inf)</t>
         </is>
       </c>
       <c r="G111" s="4" t="n">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>00_[-inf, -1.23)</t>
+          <t>00_[-inf, -1.2323)</t>
         </is>
       </c>
       <c r="G113" s="4" t="n">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>01_[-1.23, -0.766)</t>
+          <t>01_[-1.2323, -0.7665)</t>
         </is>
       </c>
       <c r="G114" s="4" t="n">
@@ -14599,7 +14599,7 @@
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>02_[-0.766, 1.41)</t>
+          <t>02_[-0.7665, 1.4143)</t>
         </is>
       </c>
       <c r="G115" s="4" t="n">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>03_[1.41, inf)</t>
+          <t>03_[1.4143, inf)</t>
         </is>
       </c>
       <c r="G116" s="4" t="n">
@@ -14830,7 +14830,7 @@
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>00_[-inf, -1.23)</t>
+          <t>00_[-inf, -1.2323)</t>
         </is>
       </c>
       <c r="G118" s="4" t="n">
@@ -14907,7 +14907,7 @@
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>01_[-1.23, -0.766)</t>
+          <t>01_[-1.2323, -0.7665)</t>
         </is>
       </c>
       <c r="G119" s="4" t="n">
@@ -14984,7 +14984,7 @@
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>02_[-0.766, 1.41)</t>
+          <t>02_[-0.7665, 1.4143)</t>
         </is>
       </c>
       <c r="G120" s="4" t="n">
@@ -15061,7 +15061,7 @@
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>03_[1.41, inf)</t>
+          <t>03_[1.4143, inf)</t>
         </is>
       </c>
       <c r="G121" s="4" t="n">
@@ -15215,7 +15215,7 @@
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>00_[-inf, -1.23)</t>
+          <t>00_[-inf, -1.2323)</t>
         </is>
       </c>
       <c r="G123" s="4" t="n">
@@ -15292,7 +15292,7 @@
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>01_[-1.23, -0.766)</t>
+          <t>01_[-1.2323, -0.7665)</t>
         </is>
       </c>
       <c r="G124" s="4" t="n">
@@ -15369,7 +15369,7 @@
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>02_[-0.766, 1.41)</t>
+          <t>02_[-0.7665, 1.4143)</t>
         </is>
       </c>
       <c r="G125" s="4" t="n">
@@ -15446,7 +15446,7 @@
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>03_[1.41, inf)</t>
+          <t>03_[1.4143, inf)</t>
         </is>
       </c>
       <c r="G126" s="4" t="n">

--- a/src/final_selected_features_report_0323.xlsx
+++ b/src/final_selected_features_report_0323.xlsx
@@ -9009,7 +9009,7 @@
         <v>0.005836575875475026</v>
       </c>
       <c r="P42" s="33" t="n">
-        <v>0.001736087251765193</v>
+        <v>0.001736087251765199</v>
       </c>
       <c r="Q42" s="33" t="n">
         <v>16.12715889808134</v>
@@ -9163,7 +9163,7 @@
         <v>0.01429772918417637</v>
       </c>
       <c r="P44" s="33" t="n">
-        <v>0.001128377915005525</v>
+        <v>0.001128377915005526</v>
       </c>
       <c r="Q44" s="33" t="n">
         <v>33.91251998147218</v>
@@ -9240,7 +9240,7 @@
         <v>0.02292650033713896</v>
       </c>
       <c r="P45" s="33" t="n">
-        <v>0.003257163253097077</v>
+        <v>0.003257163253097072</v>
       </c>
       <c r="Q45" s="33" t="n">
         <v>37.98175887919754</v>
@@ -9317,7 +9317,7 @@
         <v>0.02731929425154962</v>
       </c>
       <c r="P46" s="33" t="n">
-        <v>0.0007123663543206845</v>
+        <v>0.0007123663543206875</v>
       </c>
       <c r="Q46" s="33" t="n">
         <v>42.39599625914426</v>
@@ -9394,7 +9394,7 @@
         <v>0.03734827264237285</v>
       </c>
       <c r="P47" s="33" t="n">
-        <v>3.459965780581173e-05</v>
+        <v>3.459965780581079e-05</v>
       </c>
       <c r="Q47" s="33" t="n">
         <v>44.44014271251836</v>
@@ -9471,7 +9471,7 @@
         <v>0.0470637234485435</v>
       </c>
       <c r="P48" s="33" t="n">
-        <v>6.830132726200356e-05</v>
+        <v>6.830132726200289e-05</v>
       </c>
       <c r="Q48" s="33" t="n">
         <v>38.03506957265319</v>
@@ -9625,7 +9625,7 @@
         <v>0.09472934472931099</v>
       </c>
       <c r="P50" s="33" t="n">
-        <v>0.0004696197169115956</v>
+        <v>0.0004696197169115931</v>
       </c>
       <c r="Q50" s="33" t="n">
         <v>2.706069257563115e-07</v>
@@ -9856,7 +9856,7 @@
         <v>0.004135079255682884</v>
       </c>
       <c r="P53" s="33" t="n">
-        <v>0.0001896821127372343</v>
+        <v>0.0001896821127372322</v>
       </c>
       <c r="Q53" s="33" t="n">
         <v>15.36193203141119</v>
@@ -10010,7 +10010,7 @@
         <v>0.01297203805130788</v>
       </c>
       <c r="P55" s="33" t="n">
-        <v>0.0005573466185521162</v>
+        <v>0.0005573466185521136</v>
       </c>
       <c r="Q55" s="33" t="n">
         <v>33.19767422518643</v>
@@ -10087,7 +10087,7 @@
         <v>0.01938683498646993</v>
       </c>
       <c r="P56" s="33" t="n">
-        <v>0.0008084235937556063</v>
+        <v>0.0008084235937556085</v>
       </c>
       <c r="Q56" s="33" t="n">
         <v>39.17578112312736</v>
@@ -10164,7 +10164,7 @@
         <v>0.02330913259456948</v>
       </c>
       <c r="P57" s="33" t="n">
-        <v>0.0002504848115393414</v>
+        <v>0.0002504848115393406</v>
       </c>
       <c r="Q57" s="33" t="n">
         <v>43.85981938831623</v>
@@ -10241,7 +10241,7 @@
         <v>0.03508498362700217</v>
       </c>
       <c r="P58" s="33" t="n">
-        <v>6.867588621114581e-08</v>
+        <v>6.867588621118701e-08</v>
       </c>
       <c r="Q58" s="33" t="n">
         <v>45.0457889952698</v>
@@ -10318,7 +10318,7 @@
         <v>0.04557454494927809</v>
       </c>
       <c r="P59" s="33" t="n">
-        <v>5.174740399682864e-05</v>
+        <v>5.174740399682921e-05</v>
       </c>
       <c r="Q59" s="33" t="n">
         <v>41.52024086651192</v>
@@ -10472,7 +10472,7 @@
         <v>0.09574970484060262</v>
       </c>
       <c r="P61" s="33" t="n">
-        <v>0.0002221892993538959</v>
+        <v>0.0002221892993538976</v>
       </c>
       <c r="Q61" s="33" t="n">
         <v>9.299511161131591e-08</v>
@@ -10626,7 +10626,7 @@
         <v>0.09609999999999039</v>
       </c>
       <c r="P63" s="33" t="n">
-        <v>0.002182734856492598</v>
+        <v>0.002182734856492597</v>
       </c>
       <c r="Q63" s="33" t="n">
         <v>45.0457889952698</v>
